--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2023-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2023-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0870AE96-13D4-4195-82F8-8DD42B585B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F638197F-6CA8-4E73-8AE5-5329313A1A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{FB483F05-ECDD-4581-B5D6-C061736F8B0D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{8C8C5979-D68C-456B-91EA-F90EEA849816}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1577,29 +1577,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219603E3-DB4D-4317-9DA7-99B23009871C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7DC6FE-5C37-4401-AF1A-60C170093DDB}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1633,7 +1632,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1669,7 +1668,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1721,7 +1720,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1789,7 +1788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1861,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="17" t="s">
@@ -1961,7 +1960,7 @@
       <c r="W7" s="49"/>
       <c r="X7" s="45"/>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2022</v>
       </c>
@@ -2033,7 +2032,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="40">
         <v>2021</v>
       </c>
@@ -2105,7 +2104,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="42"/>
       <c r="B10" s="43"/>
       <c r="C10" s="17" t="s">
@@ -2133,7 +2132,7 @@
       <c r="W10" s="49"/>
       <c r="X10" s="45"/>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2020</v>
       </c>
@@ -2205,7 +2204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="50">
         <v>2019</v>
       </c>
@@ -2277,7 +2276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2018</v>
       </c>
@@ -2349,7 +2348,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="50">
         <v>2017</v>
       </c>
@@ -2421,7 +2420,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2016</v>
       </c>
@@ -2493,7 +2492,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="50">
         <v>2015</v>
       </c>
@@ -2565,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2014</v>
       </c>
@@ -2637,7 +2636,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="50">
         <v>2013</v>
       </c>
@@ -2709,7 +2708,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2012</v>
       </c>
@@ -2781,7 +2780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="50">
         <v>2011</v>
       </c>
@@ -2853,7 +2852,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2010</v>
       </c>
@@ -2925,7 +2924,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="50">
         <v>2009</v>
       </c>
@@ -2997,7 +2996,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2008</v>
       </c>
@@ -3069,7 +3068,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2007</v>
       </c>
@@ -3141,7 +3140,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="42"/>
       <c r="B25" s="43"/>
       <c r="C25" s="17" t="s">
@@ -3169,7 +3168,7 @@
       <c r="W25" s="49"/>
       <c r="X25" s="45"/>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="52">
         <v>2006</v>
       </c>
@@ -3241,7 +3240,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="54"/>
       <c r="B27" s="55"/>
       <c r="C27" s="21" t="s">
@@ -3269,7 +3268,7 @@
       <c r="W27" s="61"/>
       <c r="X27" s="57"/>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2005</v>
       </c>
@@ -3341,7 +3340,7 @@
         <v>9.35</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="42"/>
       <c r="B29" s="43"/>
       <c r="C29" s="17" t="s">
@@ -3369,7 +3368,7 @@
       <c r="W29" s="49"/>
       <c r="X29" s="45"/>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="52">
         <v>2004</v>
       </c>
@@ -3441,7 +3440,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="54"/>
       <c r="B31" s="55"/>
       <c r="C31" s="21" t="s">
@@ -3469,7 +3468,7 @@
       <c r="W31" s="61"/>
       <c r="X31" s="57"/>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="50">
         <v>2003</v>
       </c>
@@ -3541,7 +3540,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="52">
         <v>2002</v>
       </c>
@@ -3613,7 +3612,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="54"/>
       <c r="B34" s="55"/>
       <c r="C34" s="21" t="s">
@@ -3641,7 +3640,7 @@
       <c r="W34" s="61"/>
       <c r="X34" s="57"/>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="50">
         <v>2001</v>
       </c>
@@ -3713,7 +3712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>2000</v>
       </c>
@@ -3785,7 +3784,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="50">
         <v>1999</v>
       </c>
@@ -3857,7 +3856,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>1998</v>
       </c>
@@ -3929,7 +3928,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="50">
         <v>1997</v>
       </c>
@@ -4001,7 +4000,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="38">
         <v>1996</v>
       </c>
@@ -4073,7 +4072,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="50">
         <v>1995</v>
       </c>
@@ -4145,7 +4144,7 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="38">
         <v>1994</v>
       </c>
@@ -4217,7 +4216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="50">
         <v>1993</v>
       </c>
@@ -4289,7 +4288,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="38">
         <v>1992</v>
       </c>
@@ -4361,7 +4360,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="50" t="s">
         <v>60</v>
       </c>
